--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252040</v>
+        <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,34 +1316,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trutmyran, Vb</t>
+          <t>Brännfors, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780431</v>
+        <v>780297</v>
       </c>
       <c r="R8" t="n">
-        <v>7241554</v>
+        <v>7241829</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,12 +1370,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,27 +1395,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252040</t>
+          <t>https://artportalen.se/Sighting/136858400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252041</v>
+        <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,34 +1423,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trutmyran, Vb</t>
+          <t>Brännfors, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780441</v>
+        <v>780376</v>
       </c>
       <c r="R9" t="n">
-        <v>7241547</v>
+        <v>7241798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,12 +1477,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1492,62 +1502,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252041</t>
+          <t>https://artportalen.se/Sighting/136858401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252036</v>
+        <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>80336</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Trutmyran, Vb</t>
+          <t>Brännfors, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780412</v>
+        <v>780414</v>
       </c>
       <c r="R10" t="n">
-        <v>7241695</v>
+        <v>7241762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,12 +1584,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,70 +1609,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252036</t>
+          <t>https://artportalen.se/Sighting/136858402</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252034</v>
+        <v>121252040</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780223</v>
+        <v>780431</v>
       </c>
       <c r="R11" t="n">
-        <v>7241946</v>
+        <v>7241554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,11 +1699,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1720,59 +1722,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252034</t>
+          <t>https://artportalen.se/Sighting/121252040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252035</v>
+        <v>121252041</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780451</v>
+        <v>780441</v>
       </c>
       <c r="R12" t="n">
-        <v>7241569</v>
+        <v>7241547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,59 +1824,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252035</t>
+          <t>https://artportalen.se/Sighting/121252041</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252030</v>
+        <v>121252036</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>80336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780156</v>
+        <v>780412</v>
       </c>
       <c r="R13" t="n">
-        <v>7241427</v>
+        <v>7241695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,11 +1903,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1945,33 +1926,33 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252030</t>
+          <t>https://artportalen.se/Sighting/121252036</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252031</v>
+        <v>121252034</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1994,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780129</v>
+        <v>780223</v>
       </c>
       <c r="R14" t="n">
-        <v>7241443</v>
+        <v>7241946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2015,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,33 +2041,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252031</t>
+          <t>https://artportalen.se/Sighting/121252034</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252032</v>
+        <v>121252035</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2099,7 +2080,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2109,10 +2090,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780074</v>
+        <v>780451</v>
       </c>
       <c r="R15" t="n">
-        <v>7241491</v>
+        <v>7241569</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,16 +2151,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252032</t>
+          <t>https://artportalen.se/Sighting/121252035</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252033</v>
+        <v>121252030</v>
       </c>
       <c r="B16" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,34 +2168,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780312</v>
+        <v>780156</v>
       </c>
       <c r="R16" t="n">
-        <v>7241400</v>
+        <v>7241427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,6 +2238,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2272,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252033</t>
+          <t>https://artportalen.se/Sighting/121252030</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252037</v>
+        <v>121252031</v>
       </c>
       <c r="B17" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,34 +2283,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780297</v>
+        <v>780129</v>
       </c>
       <c r="R17" t="n">
-        <v>7241876</v>
+        <v>7241443</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2353,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2374,16 +2381,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252037</t>
+          <t>https://artportalen.se/Sighting/121252031</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252038</v>
+        <v>121252032</v>
       </c>
       <c r="B18" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,34 +2398,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780455</v>
+        <v>780074</v>
       </c>
       <c r="R18" t="n">
-        <v>7241619</v>
+        <v>7241491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,16 +2491,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121252038</t>
+          <t>https://artportalen.se/Sighting/121252032</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121252039</v>
+        <v>121252033</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780459</v>
+        <v>780312</v>
       </c>
       <c r="R19" t="n">
-        <v>7241605</v>
+        <v>7241400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,6 +2592,312 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252033</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121252037</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Trutmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>780297</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7241876</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252037</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121252038</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trutmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>780455</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7241619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252038</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121252039</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Trutmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>780459</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7241605</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121252039</t>
         </is>
@@ -2602,6 +2923,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>136858400</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136858401</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136858402</v>
       </c>
       <c r="B10" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
